--- a/docentes/Rodríguez Román Leticia - Estadisticos 20221.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="134">
   <si>
     <t>Mat</t>
   </si>
@@ -76,34 +76,115 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>BAROJAS</t>
+  </si>
+  <si>
+    <t>LOYO</t>
+  </si>
+  <si>
+    <t>MOLOHUA</t>
+  </si>
+  <si>
     <t>SAN JUAN</t>
   </si>
   <si>
+    <t>TERCERO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>MATLATECATL</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
     <t>TZITZIHUA</t>
   </si>
   <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>TERCERO</t>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
+    <t>ARGÜELLO</t>
+  </si>
+  <si>
+    <t>ESPINOZA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>MADRAZO</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
   </si>
   <si>
     <t>VARGAS</t>
   </si>
   <si>
-    <t>MATLATECATL</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>MADRIGAL</t>
+  </si>
+  <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
+    <t>CHULIN</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
   </si>
   <si>
     <t>PEREZ</t>
@@ -112,244 +193,232 @@
     <t>VENTURA</t>
   </si>
   <si>
+    <t>MONGE</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>AGUILAR</t>
   </si>
   <si>
-    <t>ARGÜELLO</t>
-  </si>
-  <si>
-    <t>ESPINOZA</t>
-  </si>
-  <si>
-    <t>HIDALGO</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>TZOPITL</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>NARANJO</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>VICENTE</t>
+  </si>
+  <si>
+    <t>SORIANO</t>
+  </si>
+  <si>
+    <t>CORTES</t>
   </si>
   <si>
     <t>CASTRO</t>
   </si>
   <si>
-    <t>CHULIN</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
+    <t>DE GANTE</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>PORTILLA</t>
   </si>
   <si>
     <t>RICO</t>
   </si>
   <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>VICENTE</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>TZOPITL</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
+    <t>DEL ROSARIO</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
   </si>
   <si>
     <t>ROSALES</t>
   </si>
   <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>NARANJO</t>
-  </si>
-  <si>
-    <t>ARCADIO</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>PORTILLA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>DEL ROSARIO</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
-    <t>PIEDRAS</t>
+    <t>MARIEL</t>
+  </si>
+  <si>
+    <t>DIEGO ARMANDO</t>
+  </si>
+  <si>
+    <t>YAHIR</t>
   </si>
   <si>
     <t>ANGEL FIDEL</t>
   </si>
   <si>
+    <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>LORENA</t>
+  </si>
+  <si>
+    <t>LIZBETH JOSELYN</t>
+  </si>
+  <si>
+    <t>DULCE DANIELA</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>JOSE ALEJANDRO</t>
+  </si>
+  <si>
+    <t>CRISTIAN ALEXIS</t>
+  </si>
+  <si>
+    <t>CRISTIAN FERNANDO</t>
+  </si>
+  <si>
     <t>ADALY</t>
   </si>
   <si>
-    <t>JESUS EMMANUEL</t>
+    <t>YARELI</t>
+  </si>
+  <si>
+    <t>ATZIN HEFZIBA</t>
+  </si>
+  <si>
+    <t>SUGHEYDI JAZMIN</t>
+  </si>
+  <si>
+    <t>LIZBETH</t>
   </si>
   <si>
     <t>ESTEFANIA</t>
   </si>
   <si>
-    <t>MARIA DEL CARMEN</t>
+    <t>NADIA</t>
+  </si>
+  <si>
+    <t>VENUS</t>
+  </si>
+  <si>
+    <t>ANGELO RENE</t>
+  </si>
+  <si>
+    <t>ANGELINA</t>
+  </si>
+  <si>
+    <t>DULCE MARIA</t>
+  </si>
+  <si>
+    <t>DUILIO</t>
+  </si>
+  <si>
+    <t>JAQUELINE</t>
+  </si>
+  <si>
+    <t>BETHSABE</t>
+  </si>
+  <si>
+    <t>RICARDO</t>
+  </si>
+  <si>
+    <t>FERNANDO</t>
   </si>
   <si>
     <t>MAGDA SARAY</t>
   </si>
   <si>
-    <t>LORENA</t>
-  </si>
-  <si>
-    <t>DULCE DANIELA</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
-    <t>JOSE ALEJANDRO</t>
+    <t>KARLA GRISELL</t>
+  </si>
+  <si>
+    <t>YARETZI VALERIA</t>
+  </si>
+  <si>
+    <t>JESUS MANUEL</t>
+  </si>
+  <si>
+    <t>LAURA EVELYN</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>ARANZA DANAE</t>
+  </si>
+  <si>
+    <t>AMERICA PAOLA</t>
+  </si>
+  <si>
+    <t>CITLALI</t>
+  </si>
+  <si>
+    <t>GETSEMANI GUADALUPE</t>
+  </si>
+  <si>
+    <t>YAEL</t>
+  </si>
+  <si>
+    <t>CESAR SAID</t>
+  </si>
+  <si>
+    <t>JASIEL</t>
+  </si>
+  <si>
+    <t>GREGORIO</t>
+  </si>
+  <si>
+    <t>WENCESLAO</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
   </si>
   <si>
     <t>ANGEL DANIEL</t>
   </si>
   <si>
     <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>CRISTHIAN</t>
-  </si>
-  <si>
-    <t>ATZIN HEFZIBA</t>
-  </si>
-  <si>
-    <t>SUGHEYDI JAZMIN</t>
-  </si>
-  <si>
-    <t>ANA LILIANA</t>
-  </si>
-  <si>
-    <t>VENUS</t>
-  </si>
-  <si>
-    <t>ANGELINA</t>
-  </si>
-  <si>
-    <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>BETHSABE</t>
-  </si>
-  <si>
-    <t>FERNANDO</t>
-  </si>
-  <si>
-    <t>JESUS MANUEL</t>
-  </si>
-  <si>
-    <t>ARANZA DANAE</t>
-  </si>
-  <si>
-    <t>GETSEMANI GUADALUPE</t>
-  </si>
-  <si>
-    <t>YAEL</t>
-  </si>
-  <si>
-    <t>PEDRO EVER</t>
-  </si>
-  <si>
-    <t>JORGE GUILLERMO</t>
-  </si>
-  <si>
-    <t>CESAR SAID</t>
-  </si>
-  <si>
-    <t>JASIEL</t>
-  </si>
-  <si>
-    <t>WENCESLAO</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>DIEGO HUMBERTO</t>
-  </si>
-  <si>
-    <t>SINAI ANTONIO</t>
-  </si>
-  <si>
-    <t>JORGE MARIO</t>
-  </si>
-  <si>
-    <t>LUIS REY</t>
   </si>
 </sst>
 </file>
@@ -825,22 +894,22 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F5">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="G5">
-        <v>37.5</v>
+        <v>61.29</v>
       </c>
       <c r="H5">
-        <v>6.9</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -893,16 +962,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>68.75</v>
+      </c>
+      <c r="H2">
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -916,16 +988,19 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>51.22</v>
+      </c>
+      <c r="H3">
+        <v>6.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -939,16 +1014,19 @@
         <v>39</v>
       </c>
       <c r="D4">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>61.54</v>
+      </c>
+      <c r="H4">
+        <v>6.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -959,19 +1037,22 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>58.06</v>
+      </c>
+      <c r="H5">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1027,16 +1108,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>78.13</v>
+        <v>68.75</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1053,16 +1134,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G3">
-        <v>70.73</v>
+        <v>51.22</v>
       </c>
       <c r="H3">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1079,16 +1160,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F4">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G4">
-        <v>74.36</v>
+        <v>61.54</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1099,22 +1180,22 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F5">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G5">
-        <v>37.5</v>
+        <v>58.06</v>
       </c>
       <c r="H5">
-        <v>6.9</v>
+        <v>6.1</v>
       </c>
     </row>
   </sheetData>
@@ -1124,7 +1205,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1156,16 +1237,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920177</v>
+        <v>21330051920154</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1179,16 +1260,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920181</v>
+        <v>21330051920164</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="D3" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1202,22 +1283,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920255</v>
+        <v>21330051920171</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1225,22 +1306,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920081</v>
+        <v>21330051920177</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1254,10 +1335,10 @@
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1271,22 +1352,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920286</v>
+        <v>21330051920234</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1294,16 +1375,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920234</v>
+        <v>21330051920235</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1320,13 +1401,13 @@
         <v>21330051920240</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
         <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1343,13 +1424,13 @@
         <v>19330061430023</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D10" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1363,16 +1444,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920195</v>
+        <v>21330051920202</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D11" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1386,91 +1467,91 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920202</v>
+        <v>21330051920152</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D12" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920203</v>
+        <v>21330051920162</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="D13" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920213</v>
+        <v>21330051920181</v>
       </c>
       <c r="B14" t="s">
         <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="D14" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920153</v>
+        <v>21330051920251</v>
       </c>
       <c r="B15" t="s">
         <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="D15" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1484,10 +1565,10 @@
         <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D16" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1507,10 +1588,10 @@
         <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D17" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1524,16 +1605,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920262</v>
+        <v>21330051920257</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D18" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1547,16 +1628,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920264</v>
+        <v>21330051920081</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D19" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1570,16 +1651,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920088</v>
+        <v>21330051920263</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D20" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1593,16 +1674,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21330051920358</v>
+        <v>21330051920264</v>
       </c>
       <c r="B21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C21" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="D21" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1616,16 +1697,13 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>21330051920280</v>
+        <v>21330051920267</v>
       </c>
       <c r="B22" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" t="s">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="D22" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1639,16 +1717,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>21330051920285</v>
+        <v>21330051920088</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C23" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="D23" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -1662,22 +1740,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>21330051920219</v>
+        <v>21330051920358</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C24" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="D24" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1685,22 +1763,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>21330051920044</v>
+        <v>21330051920361</v>
       </c>
       <c r="B25" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="C25" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="D25" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1708,22 +1786,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>21330051920250</v>
+        <v>21330051920362</v>
       </c>
       <c r="B26" t="s">
         <v>41</v>
       </c>
       <c r="C26" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D26" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -1731,22 +1809,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>21330051920222</v>
+        <v>21330051920280</v>
       </c>
       <c r="B27" t="s">
         <v>42</v>
       </c>
       <c r="C27" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D27" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -1754,22 +1832,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>21330051920186</v>
+        <v>21330051920284</v>
       </c>
       <c r="B28" t="s">
         <v>43</v>
       </c>
       <c r="C28" t="s">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="D28" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -1777,22 +1855,22 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>21330051920190</v>
+        <v>21330051920285</v>
       </c>
       <c r="B29" t="s">
         <v>44</v>
       </c>
       <c r="C29" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D29" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -1800,22 +1878,22 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>21330051920192</v>
+        <v>21330051920286</v>
       </c>
       <c r="B30" t="s">
         <v>45</v>
       </c>
       <c r="C30" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="D30" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
       </c>
       <c r="F30" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -1823,22 +1901,22 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>21330051920193</v>
+        <v>20330051920358</v>
       </c>
       <c r="B31" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="C31" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="D31" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
       </c>
       <c r="F31" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -1846,22 +1924,22 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>21330051920199</v>
+        <v>21330051920218</v>
       </c>
       <c r="B32" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="C32" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="D32" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -1869,22 +1947,22 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>21330051920201</v>
+        <v>21330051920219</v>
       </c>
       <c r="B33" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C33" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="D33" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -1892,22 +1970,22 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>21330051920205</v>
+        <v>21330051920220</v>
       </c>
       <c r="B34" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D34" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
       </c>
       <c r="F34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -1915,22 +1993,22 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>21330051920207</v>
+        <v>21330051920230</v>
       </c>
       <c r="B35" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C35" t="s">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="D35" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
       </c>
       <c r="F35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -1938,22 +2016,22 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>21330051920209</v>
+        <v>21330051920044</v>
       </c>
       <c r="B36" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="C36" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="D36" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
       </c>
       <c r="F36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -1961,24 +2039,254 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>21330051920212</v>
+        <v>21330051920239</v>
       </c>
       <c r="B37" t="s">
         <v>50</v>
       </c>
       <c r="C37" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="D37" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
       </c>
       <c r="F37" t="s">
+        <v>11</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
+        <v>21330051920247</v>
+      </c>
+      <c r="B38" t="s">
+        <v>51</v>
+      </c>
+      <c r="C38" t="s">
+        <v>82</v>
+      </c>
+      <c r="D38" t="s">
+        <v>124</v>
+      </c>
+      <c r="E38" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" t="s">
+        <v>11</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
+        <v>21330051920250</v>
+      </c>
+      <c r="B39" t="s">
+        <v>46</v>
+      </c>
+      <c r="C39" t="s">
+        <v>83</v>
+      </c>
+      <c r="D39" t="s">
+        <v>125</v>
+      </c>
+      <c r="E39" t="s">
+        <v>8</v>
+      </c>
+      <c r="F39" t="s">
+        <v>11</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40">
+        <v>21330051920222</v>
+      </c>
+      <c r="B40" t="s">
+        <v>52</v>
+      </c>
+      <c r="C40" t="s">
+        <v>39</v>
+      </c>
+      <c r="D40" t="s">
+        <v>126</v>
+      </c>
+      <c r="E40" t="s">
+        <v>8</v>
+      </c>
+      <c r="F40" t="s">
+        <v>11</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41">
+        <v>21330051920192</v>
+      </c>
+      <c r="B41" t="s">
+        <v>53</v>
+      </c>
+      <c r="C41" t="s">
+        <v>84</v>
+      </c>
+      <c r="D41" t="s">
+        <v>127</v>
+      </c>
+      <c r="E41" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41" t="s">
         <v>12</v>
       </c>
-      <c r="G37">
+      <c r="G41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42">
+        <v>21330051920193</v>
+      </c>
+      <c r="B42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C42" t="s">
+        <v>85</v>
+      </c>
+      <c r="D42" t="s">
+        <v>128</v>
+      </c>
+      <c r="E42" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42" t="s">
+        <v>12</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43">
+        <v>21330051920386</v>
+      </c>
+      <c r="B43" t="s">
+        <v>54</v>
+      </c>
+      <c r="C43" t="s">
+        <v>81</v>
+      </c>
+      <c r="D43" t="s">
+        <v>129</v>
+      </c>
+      <c r="E43" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" t="s">
+        <v>12</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44">
+        <v>21330051920199</v>
+      </c>
+      <c r="B44" t="s">
+        <v>39</v>
+      </c>
+      <c r="C44" t="s">
+        <v>73</v>
+      </c>
+      <c r="D44" t="s">
+        <v>130</v>
+      </c>
+      <c r="E44" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" t="s">
+        <v>12</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45">
+        <v>21330051920201</v>
+      </c>
+      <c r="B45" t="s">
+        <v>55</v>
+      </c>
+      <c r="C45" t="s">
+        <v>86</v>
+      </c>
+      <c r="D45" t="s">
+        <v>131</v>
+      </c>
+      <c r="E45" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" t="s">
+        <v>12</v>
+      </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46">
+        <v>21330051920203</v>
+      </c>
+      <c r="B46" t="s">
+        <v>56</v>
+      </c>
+      <c r="C46" t="s">
+        <v>67</v>
+      </c>
+      <c r="D46" t="s">
+        <v>132</v>
+      </c>
+      <c r="E46" t="s">
+        <v>8</v>
+      </c>
+      <c r="F46" t="s">
+        <v>12</v>
+      </c>
+      <c r="G46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47">
+        <v>21330051920213</v>
+      </c>
+      <c r="B47" t="s">
+        <v>57</v>
+      </c>
+      <c r="C47" t="s">
+        <v>87</v>
+      </c>
+      <c r="D47" t="s">
+        <v>133</v>
+      </c>
+      <c r="E47" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" t="s">
+        <v>12</v>
+      </c>
+      <c r="G47">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rodríguez Román Leticia - Estadisticos 20221.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="133">
   <si>
     <t>Mat</t>
   </si>
@@ -91,39 +91,39 @@
     <t>TERCERO</t>
   </si>
   <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>MATLATECATL</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>TZITZIHUA</t>
+  </si>
+  <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
+    <t>ARGÜELLO</t>
+  </si>
+  <si>
+    <t>ESPINOZA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>MATLATECATL</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>TZITZIHUA</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>ARGÜELLO</t>
-  </si>
-  <si>
-    <t>ESPINOZA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>DE JESUS</t>
   </si>
   <si>
@@ -296,9 +296,6 @@
   </si>
   <si>
     <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>LORENA</t>
   </si>
   <si>
     <t>LIZBETH JOSELYN</t>
@@ -1205,7 +1202,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1352,13 +1349,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920234</v>
+        <v>21330051920235</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D7" t="s">
         <v>93</v>
@@ -1375,13 +1372,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920235</v>
+        <v>21330051920240</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
         <v>94</v>
@@ -1398,13 +1395,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920240</v>
+        <v>19330061430023</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="D9" t="s">
         <v>95</v>
@@ -1413,7 +1410,7 @@
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1421,13 +1418,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330061430023</v>
+        <v>21330051920202</v>
       </c>
       <c r="B10" t="s">
         <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D10" t="s">
         <v>96</v>
@@ -1444,13 +1441,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920202</v>
+        <v>21330051920152</v>
       </c>
       <c r="B11" t="s">
         <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D11" t="s">
         <v>97</v>
@@ -1459,21 +1456,21 @@
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920152</v>
+        <v>21330051920162</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s">
         <v>98</v>
@@ -1490,13 +1487,13 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920162</v>
+        <v>21330051920181</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D13" t="s">
         <v>99</v>
@@ -1513,13 +1510,13 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920181</v>
+        <v>21330051920251</v>
       </c>
       <c r="B14" t="s">
         <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="D14" t="s">
         <v>100</v>
@@ -1528,7 +1525,7 @@
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1536,13 +1533,13 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920251</v>
+        <v>21330051920253</v>
       </c>
       <c r="B15" t="s">
         <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D15" t="s">
         <v>101</v>
@@ -1559,13 +1556,13 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920253</v>
+        <v>21330051920256</v>
       </c>
       <c r="B16" t="s">
         <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D16" t="s">
         <v>102</v>
@@ -1582,13 +1579,13 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920256</v>
+        <v>21330051920257</v>
       </c>
       <c r="B17" t="s">
         <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="s">
         <v>103</v>
@@ -1605,13 +1602,13 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920257</v>
+        <v>21330051920081</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D18" t="s">
         <v>104</v>
@@ -1628,13 +1625,13 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920081</v>
+        <v>21330051920263</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D19" t="s">
         <v>105</v>
@@ -1651,13 +1648,13 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920263</v>
+        <v>21330051920264</v>
       </c>
       <c r="B20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C20" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D20" t="s">
         <v>106</v>
@@ -1674,13 +1671,10 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21330051920264</v>
+        <v>21330051920267</v>
       </c>
       <c r="B21" t="s">
-        <v>36</v>
-      </c>
-      <c r="C21" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="D21" t="s">
         <v>107</v>
@@ -1697,10 +1691,13 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>21330051920267</v>
+        <v>21330051920088</v>
       </c>
       <c r="B22" t="s">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="C22" t="s">
+        <v>24</v>
       </c>
       <c r="D22" t="s">
         <v>108</v>
@@ -1717,13 +1714,13 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>21330051920088</v>
+        <v>21330051920358</v>
       </c>
       <c r="B23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D23" t="s">
         <v>109</v>
@@ -1740,13 +1737,13 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>21330051920358</v>
+        <v>21330051920361</v>
       </c>
       <c r="B24" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="D24" t="s">
         <v>110</v>
@@ -1763,13 +1760,13 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>21330051920361</v>
+        <v>21330051920362</v>
       </c>
       <c r="B25" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C25" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="D25" t="s">
         <v>111</v>
@@ -1786,13 +1783,13 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>21330051920362</v>
+        <v>21330051920280</v>
       </c>
       <c r="B26" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C26" t="s">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="D26" t="s">
         <v>112</v>
@@ -1809,13 +1806,13 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>21330051920280</v>
+        <v>21330051920284</v>
       </c>
       <c r="B27" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C27" t="s">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="D27" t="s">
         <v>113</v>
@@ -1832,13 +1829,13 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>21330051920284</v>
+        <v>21330051920285</v>
       </c>
       <c r="B28" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C28" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D28" t="s">
         <v>114</v>
@@ -1855,13 +1852,13 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>21330051920285</v>
+        <v>21330051920286</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C29" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D29" t="s">
         <v>115</v>
@@ -1878,13 +1875,13 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>21330051920286</v>
+        <v>20330051920358</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C30" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D30" t="s">
         <v>116</v>
@@ -1901,13 +1898,13 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>20330051920358</v>
+        <v>21330051920218</v>
       </c>
       <c r="B31" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C31" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D31" t="s">
         <v>117</v>
@@ -1916,7 +1913,7 @@
         <v>8</v>
       </c>
       <c r="F31" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -1924,13 +1921,13 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>21330051920218</v>
+        <v>21330051920219</v>
       </c>
       <c r="B32" t="s">
         <v>47</v>
       </c>
       <c r="C32" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="D32" t="s">
         <v>118</v>
@@ -1947,13 +1944,13 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>21330051920219</v>
+        <v>21330051920220</v>
       </c>
       <c r="B33" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C33" t="s">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="D33" t="s">
         <v>119</v>
@@ -1970,13 +1967,13 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>21330051920220</v>
+        <v>21330051920230</v>
       </c>
       <c r="B34" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C34" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D34" t="s">
         <v>120</v>
@@ -1993,13 +1990,13 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>21330051920230</v>
+        <v>21330051920044</v>
       </c>
       <c r="B35" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="C35" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D35" t="s">
         <v>121</v>
@@ -2016,13 +2013,13 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>21330051920044</v>
+        <v>21330051920239</v>
       </c>
       <c r="B36" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="C36" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D36" t="s">
         <v>122</v>
@@ -2039,13 +2036,13 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>21330051920239</v>
+        <v>21330051920247</v>
       </c>
       <c r="B37" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C37" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D37" t="s">
         <v>123</v>
@@ -2062,13 +2059,13 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>21330051920247</v>
+        <v>21330051920250</v>
       </c>
       <c r="B38" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C38" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D38" t="s">
         <v>124</v>
@@ -2085,13 +2082,13 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>21330051920250</v>
+        <v>21330051920222</v>
       </c>
       <c r="B39" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C39" t="s">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="D39" t="s">
         <v>125</v>
@@ -2108,13 +2105,13 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>21330051920222</v>
+        <v>21330051920192</v>
       </c>
       <c r="B40" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C40" t="s">
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="D40" t="s">
         <v>126</v>
@@ -2123,7 +2120,7 @@
         <v>8</v>
       </c>
       <c r="F40" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -2131,13 +2128,13 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>21330051920192</v>
+        <v>21330051920193</v>
       </c>
       <c r="B41" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="C41" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D41" t="s">
         <v>127</v>
@@ -2154,13 +2151,13 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>21330051920193</v>
+        <v>21330051920386</v>
       </c>
       <c r="B42" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="C42" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D42" t="s">
         <v>128</v>
@@ -2177,13 +2174,13 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>21330051920386</v>
+        <v>21330051920199</v>
       </c>
       <c r="B43" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="C43" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D43" t="s">
         <v>129</v>
@@ -2200,13 +2197,13 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>21330051920199</v>
+        <v>21330051920201</v>
       </c>
       <c r="B44" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="C44" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="D44" t="s">
         <v>130</v>
@@ -2223,13 +2220,13 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>21330051920201</v>
+        <v>21330051920203</v>
       </c>
       <c r="B45" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C45" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="D45" t="s">
         <v>131</v>
@@ -2246,13 +2243,13 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>21330051920203</v>
+        <v>21330051920213</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C46" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="D46" t="s">
         <v>132</v>
@@ -2264,29 +2261,6 @@
         <v>12</v>
       </c>
       <c r="G46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47">
-        <v>21330051920213</v>
-      </c>
-      <c r="B47" t="s">
-        <v>57</v>
-      </c>
-      <c r="C47" t="s">
-        <v>87</v>
-      </c>
-      <c r="D47" t="s">
-        <v>133</v>
-      </c>
-      <c r="E47" t="s">
-        <v>8</v>
-      </c>
-      <c r="F47" t="s">
-        <v>12</v>
-      </c>
-      <c r="G47">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rodríguez Román Leticia - Estadisticos 20221.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="136">
   <si>
     <t>Mat</t>
   </si>
@@ -97,6 +97,9 @@
     <t>MATLATECATL</t>
   </si>
   <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
@@ -205,6 +208,9 @@
     <t>CARRILLO</t>
   </si>
   <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
     <t>TZOPITL</t>
   </si>
   <si>
@@ -302,6 +308,9 @@
   </si>
   <si>
     <t>DULCE DANIELA</t>
+  </si>
+  <si>
+    <t>IVAN</t>
   </si>
   <si>
     <t>JOSE MANUEL</t>
@@ -1202,7 +1211,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1240,10 +1249,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1263,10 +1272,10 @@
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1286,10 +1295,10 @@
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1309,10 +1318,10 @@
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1332,10 +1341,10 @@
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1355,10 +1364,10 @@
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1378,10 +1387,10 @@
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1395,16 +1404,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330061430023</v>
+        <v>21330051920188</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1418,16 +1427,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920202</v>
+        <v>19330061430023</v>
       </c>
       <c r="B10" t="s">
         <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1441,39 +1450,39 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920152</v>
+        <v>21330051920202</v>
       </c>
       <c r="B11" t="s">
         <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D11" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920162</v>
+        <v>21330051920152</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="D12" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1487,16 +1496,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920181</v>
+        <v>21330051920162</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="D13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1510,22 +1519,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920251</v>
+        <v>21330051920181</v>
       </c>
       <c r="B14" t="s">
         <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="D14" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1533,16 +1542,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920253</v>
+        <v>21330051920251</v>
       </c>
       <c r="B15" t="s">
         <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D15" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1556,16 +1565,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920256</v>
+        <v>21330051920253</v>
       </c>
       <c r="B16" t="s">
         <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D16" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1579,16 +1588,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920257</v>
+        <v>21330051920256</v>
       </c>
       <c r="B17" t="s">
         <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1602,16 +1611,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920081</v>
+        <v>21330051920257</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D18" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1625,16 +1634,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920263</v>
+        <v>21330051920081</v>
       </c>
       <c r="B19" t="s">
         <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D19" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1648,16 +1657,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920264</v>
+        <v>21330051920263</v>
       </c>
       <c r="B20" t="s">
         <v>36</v>
       </c>
       <c r="C20" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D20" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1671,13 +1680,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21330051920267</v>
+        <v>21330051920264</v>
       </c>
       <c r="B21" t="s">
         <v>37</v>
       </c>
+      <c r="C21" t="s">
+        <v>73</v>
+      </c>
       <c r="D21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1691,16 +1703,13 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>21330051920088</v>
+        <v>21330051920267</v>
       </c>
       <c r="B22" t="s">
         <v>38</v>
       </c>
-      <c r="C22" t="s">
-        <v>24</v>
-      </c>
       <c r="D22" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1714,16 +1723,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>21330051920358</v>
+        <v>21330051920088</v>
       </c>
       <c r="B23" t="s">
         <v>39</v>
       </c>
       <c r="C23" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D23" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -1737,16 +1746,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>21330051920361</v>
+        <v>21330051920358</v>
       </c>
       <c r="B24" t="s">
         <v>40</v>
       </c>
       <c r="C24" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="D24" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -1760,16 +1769,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>21330051920362</v>
+        <v>21330051920361</v>
       </c>
       <c r="B25" t="s">
         <v>41</v>
       </c>
       <c r="C25" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="D25" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -1783,16 +1792,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>21330051920280</v>
+        <v>21330051920362</v>
       </c>
       <c r="B26" t="s">
         <v>42</v>
       </c>
       <c r="C26" t="s">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="D26" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -1806,16 +1815,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>21330051920284</v>
+        <v>21330051920280</v>
       </c>
       <c r="B27" t="s">
         <v>43</v>
       </c>
       <c r="C27" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="D27" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -1829,16 +1838,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>21330051920285</v>
+        <v>21330051920284</v>
       </c>
       <c r="B28" t="s">
         <v>44</v>
       </c>
       <c r="C28" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D28" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -1852,16 +1861,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>21330051920286</v>
+        <v>21330051920285</v>
       </c>
       <c r="B29" t="s">
         <v>45</v>
       </c>
       <c r="C29" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D29" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -1875,16 +1884,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>20330051920358</v>
+        <v>21330051920286</v>
       </c>
       <c r="B30" t="s">
         <v>46</v>
       </c>
       <c r="C30" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D30" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -1898,22 +1907,22 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>21330051920218</v>
+        <v>20330051920358</v>
       </c>
       <c r="B31" t="s">
         <v>47</v>
       </c>
       <c r="C31" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D31" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
       </c>
       <c r="F31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -1921,16 +1930,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>21330051920219</v>
+        <v>21330051920218</v>
       </c>
       <c r="B32" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C32" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="D32" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -1944,16 +1953,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>21330051920220</v>
+        <v>21330051920219</v>
       </c>
       <c r="B33" t="s">
         <v>48</v>
       </c>
       <c r="C33" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="D33" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -1967,16 +1976,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>21330051920230</v>
+        <v>21330051920220</v>
       </c>
       <c r="B34" t="s">
         <v>49</v>
       </c>
       <c r="C34" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D34" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -1990,16 +1999,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>21330051920044</v>
+        <v>21330051920230</v>
       </c>
       <c r="B35" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="C35" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D35" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -2013,16 +2022,16 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>21330051920239</v>
+        <v>21330051920044</v>
       </c>
       <c r="B36" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="C36" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D36" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
@@ -2036,16 +2045,16 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>21330051920247</v>
+        <v>21330051920239</v>
       </c>
       <c r="B37" t="s">
         <v>51</v>
       </c>
       <c r="C37" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D37" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
@@ -2059,16 +2068,16 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>21330051920250</v>
+        <v>21330051920247</v>
       </c>
       <c r="B38" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C38" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D38" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
@@ -2082,16 +2091,16 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>21330051920222</v>
+        <v>21330051920250</v>
       </c>
       <c r="B39" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C39" t="s">
-        <v>39</v>
+        <v>85</v>
       </c>
       <c r="D39" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
@@ -2105,22 +2114,22 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>21330051920192</v>
+        <v>21330051920222</v>
       </c>
       <c r="B40" t="s">
         <v>53</v>
       </c>
       <c r="C40" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="D40" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
       </c>
       <c r="F40" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -2128,16 +2137,16 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>21330051920193</v>
+        <v>21330051920192</v>
       </c>
       <c r="B41" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="C41" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D41" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
@@ -2151,16 +2160,16 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>21330051920386</v>
+        <v>21330051920193</v>
       </c>
       <c r="B42" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="C42" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D42" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
@@ -2174,16 +2183,16 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>21330051920199</v>
+        <v>21330051920386</v>
       </c>
       <c r="B43" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="C43" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="D43" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
@@ -2197,16 +2206,16 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>21330051920201</v>
+        <v>21330051920199</v>
       </c>
       <c r="B44" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="C44" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="D44" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
@@ -2220,16 +2229,16 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>21330051920203</v>
+        <v>21330051920201</v>
       </c>
       <c r="B45" t="s">
         <v>56</v>
       </c>
       <c r="C45" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="D45" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -2243,16 +2252,16 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>21330051920213</v>
+        <v>21330051920203</v>
       </c>
       <c r="B46" t="s">
         <v>57</v>
       </c>
       <c r="C46" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="D46" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
@@ -2261,6 +2270,29 @@
         <v>12</v>
       </c>
       <c r="G46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47">
+        <v>21330051920213</v>
+      </c>
+      <c r="B47" t="s">
+        <v>58</v>
+      </c>
+      <c r="C47" t="s">
+        <v>89</v>
+      </c>
+      <c r="D47" t="s">
+        <v>135</v>
+      </c>
+      <c r="E47" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" t="s">
+        <v>12</v>
+      </c>
+      <c r="G47">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rodríguez Román Leticia - Estadisticos 20221.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="139">
   <si>
     <t>Mat</t>
   </si>
@@ -82,33 +82,39 @@
     <t>LOYO</t>
   </si>
   <si>
+    <t>HIDALGO</t>
+  </si>
+  <si>
+    <t>TERCERO</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>MATLATECATL</t>
+  </si>
+  <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
     <t>MOLOHUA</t>
   </si>
   <si>
     <t>SAN JUAN</t>
   </si>
   <si>
-    <t>TERCERO</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>MATLATECATL</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
     <t>TZITZIHUA</t>
   </si>
   <si>
@@ -190,9 +196,6 @@
     <t>OFICIAL</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
     <t>VENTURA</t>
   </si>
   <si>
@@ -202,33 +205,36 @@
     <t>ROMERO</t>
   </si>
   <si>
+    <t>ARCADIO</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>TZOPITL</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
     <t>AGUILAR</t>
   </si>
   <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>TZOPITL</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
     <t>VALENCIA</t>
   </si>
   <si>
     <t>NARANJO</t>
   </si>
   <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
     <t>MENDOZA</t>
   </si>
   <si>
@@ -295,36 +301,42 @@
     <t>DIEGO ARMANDO</t>
   </si>
   <si>
+    <t>ANA LILIANA</t>
+  </si>
+  <si>
+    <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>LIZBETH JOSELYN</t>
+  </si>
+  <si>
+    <t>DULCE DANIELA</t>
+  </si>
+  <si>
+    <t>IVAN</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>JOSE ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ANGEL DANIEL</t>
+  </si>
+  <si>
+    <t>CRISTIAN ALEXIS</t>
+  </si>
+  <si>
+    <t>CRISTIAN FERNANDO</t>
+  </si>
+  <si>
     <t>YAHIR</t>
   </si>
   <si>
     <t>ANGEL FIDEL</t>
   </si>
   <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>LIZBETH JOSELYN</t>
-  </si>
-  <si>
-    <t>DULCE DANIELA</t>
-  </si>
-  <si>
-    <t>IVAN</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>JOSE ALEJANDRO</t>
-  </si>
-  <si>
-    <t>CRISTIAN ALEXIS</t>
-  </si>
-  <si>
-    <t>CRISTIAN FERNANDO</t>
-  </si>
-  <si>
     <t>ADALY</t>
   </si>
   <si>
@@ -419,9 +431,6 @@
   </si>
   <si>
     <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>ANGEL DANIEL</t>
   </si>
   <si>
     <t>GUSTAVO</t>
@@ -1211,7 +1220,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1249,10 +1258,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1272,10 +1281,10 @@
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1289,22 +1298,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920171</v>
+        <v>21330051920262</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1312,22 +1321,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920177</v>
+        <v>21330051920282</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1335,22 +1344,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920282</v>
+        <v>21330051920235</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1358,16 +1367,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920235</v>
+        <v>21330051920240</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1381,22 +1390,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920240</v>
+        <v>21330051920188</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1404,16 +1413,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920188</v>
+        <v>19330061430023</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D9" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1427,16 +1436,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330061430023</v>
+        <v>21330051920202</v>
       </c>
       <c r="B10" t="s">
         <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1450,16 +1459,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920202</v>
+        <v>21330051920203</v>
       </c>
       <c r="B11" t="s">
         <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1479,10 +1488,10 @@
         <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D12" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1499,13 +1508,13 @@
         <v>21330051920162</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D13" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1519,16 +1528,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920181</v>
+        <v>21330051920171</v>
       </c>
       <c r="B14" t="s">
         <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1542,22 +1551,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920251</v>
+        <v>21330051920177</v>
       </c>
       <c r="B15" t="s">
         <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D15" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1565,22 +1574,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920253</v>
+        <v>21330051920181</v>
       </c>
       <c r="B16" t="s">
         <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="D16" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1588,16 +1597,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920256</v>
+        <v>21330051920251</v>
       </c>
       <c r="B17" t="s">
         <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D17" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1611,16 +1620,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920257</v>
+        <v>21330051920253</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D18" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1634,16 +1643,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920081</v>
+        <v>21330051920256</v>
       </c>
       <c r="B19" t="s">
         <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D19" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1657,7 +1666,7 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920263</v>
+        <v>21330051920257</v>
       </c>
       <c r="B20" t="s">
         <v>36</v>
@@ -1666,7 +1675,7 @@
         <v>72</v>
       </c>
       <c r="D20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1680,7 +1689,7 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21330051920264</v>
+        <v>21330051920081</v>
       </c>
       <c r="B21" t="s">
         <v>37</v>
@@ -1689,7 +1698,7 @@
         <v>73</v>
       </c>
       <c r="D21" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1703,13 +1712,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>21330051920267</v>
+        <v>21330051920263</v>
       </c>
       <c r="B22" t="s">
         <v>38</v>
       </c>
+      <c r="C22" t="s">
+        <v>74</v>
+      </c>
       <c r="D22" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1723,16 +1735,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>21330051920088</v>
+        <v>21330051920264</v>
       </c>
       <c r="B23" t="s">
         <v>39</v>
       </c>
       <c r="C23" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="D23" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -1746,16 +1758,13 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>21330051920358</v>
+        <v>21330051920267</v>
       </c>
       <c r="B24" t="s">
         <v>40</v>
       </c>
-      <c r="C24" t="s">
-        <v>27</v>
-      </c>
       <c r="D24" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -1769,16 +1778,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>21330051920361</v>
+        <v>21330051920088</v>
       </c>
       <c r="B25" t="s">
         <v>41</v>
       </c>
       <c r="C25" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D25" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -1792,16 +1801,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>21330051920362</v>
+        <v>21330051920358</v>
       </c>
       <c r="B26" t="s">
         <v>42</v>
       </c>
       <c r="C26" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="D26" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -1815,16 +1824,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>21330051920280</v>
+        <v>21330051920361</v>
       </c>
       <c r="B27" t="s">
         <v>43</v>
       </c>
       <c r="C27" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="D27" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -1838,16 +1847,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>21330051920284</v>
+        <v>21330051920362</v>
       </c>
       <c r="B28" t="s">
         <v>44</v>
       </c>
       <c r="C28" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D28" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -1861,16 +1870,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>21330051920285</v>
+        <v>21330051920280</v>
       </c>
       <c r="B29" t="s">
         <v>45</v>
       </c>
       <c r="C29" t="s">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="D29" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -1884,7 +1893,7 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>21330051920286</v>
+        <v>21330051920284</v>
       </c>
       <c r="B30" t="s">
         <v>46</v>
@@ -1893,7 +1902,7 @@
         <v>77</v>
       </c>
       <c r="D30" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -1907,7 +1916,7 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>20330051920358</v>
+        <v>21330051920285</v>
       </c>
       <c r="B31" t="s">
         <v>47</v>
@@ -1916,7 +1925,7 @@
         <v>78</v>
       </c>
       <c r="D31" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -1930,7 +1939,7 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>21330051920218</v>
+        <v>21330051920286</v>
       </c>
       <c r="B32" t="s">
         <v>48</v>
@@ -1939,13 +1948,13 @@
         <v>79</v>
       </c>
       <c r="D32" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -1953,22 +1962,22 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>21330051920219</v>
+        <v>20330051920358</v>
       </c>
       <c r="B33" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C33" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="D33" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -1976,16 +1985,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>21330051920220</v>
+        <v>21330051920218</v>
       </c>
       <c r="B34" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C34" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D34" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -1999,16 +2008,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>21330051920230</v>
+        <v>21330051920219</v>
       </c>
       <c r="B35" t="s">
         <v>50</v>
       </c>
       <c r="C35" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="D35" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -2022,16 +2031,16 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>21330051920044</v>
+        <v>21330051920220</v>
       </c>
       <c r="B36" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="C36" t="s">
         <v>82</v>
       </c>
       <c r="D36" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
@@ -2045,16 +2054,16 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>21330051920239</v>
+        <v>21330051920230</v>
       </c>
       <c r="B37" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C37" t="s">
         <v>83</v>
       </c>
       <c r="D37" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
@@ -2068,16 +2077,16 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>21330051920247</v>
+        <v>21330051920044</v>
       </c>
       <c r="B38" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="C38" t="s">
         <v>84</v>
       </c>
       <c r="D38" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
@@ -2091,16 +2100,16 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>21330051920250</v>
+        <v>21330051920239</v>
       </c>
       <c r="B39" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C39" t="s">
         <v>85</v>
       </c>
       <c r="D39" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
@@ -2114,16 +2123,16 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>21330051920222</v>
+        <v>21330051920247</v>
       </c>
       <c r="B40" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C40" t="s">
-        <v>40</v>
+        <v>86</v>
       </c>
       <c r="D40" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -2137,22 +2146,22 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>21330051920192</v>
+        <v>21330051920250</v>
       </c>
       <c r="B41" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C41" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D41" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
       </c>
       <c r="F41" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G41">
         <v>1</v>
@@ -2160,22 +2169,22 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>21330051920193</v>
+        <v>21330051920222</v>
       </c>
       <c r="B42" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="C42" t="s">
-        <v>87</v>
+        <v>42</v>
       </c>
       <c r="D42" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
       </c>
       <c r="F42" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G42">
         <v>1</v>
@@ -2183,16 +2192,16 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>21330051920386</v>
+        <v>21330051920192</v>
       </c>
       <c r="B43" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C43" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D43" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
@@ -2206,16 +2215,16 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>21330051920199</v>
+        <v>21330051920193</v>
       </c>
       <c r="B44" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="C44" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="D44" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
@@ -2229,16 +2238,16 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>21330051920201</v>
+        <v>21330051920386</v>
       </c>
       <c r="B45" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C45" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D45" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -2252,16 +2261,16 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>21330051920203</v>
+        <v>21330051920199</v>
       </c>
       <c r="B46" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="C46" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="D46" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
@@ -2275,16 +2284,16 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>21330051920213</v>
+        <v>21330051920201</v>
       </c>
       <c r="B47" t="s">
         <v>58</v>
       </c>
       <c r="C47" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D47" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
@@ -2293,6 +2302,29 @@
         <v>12</v>
       </c>
       <c r="G47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48">
+        <v>21330051920213</v>
+      </c>
+      <c r="B48" t="s">
+        <v>59</v>
+      </c>
+      <c r="C48" t="s">
+        <v>91</v>
+      </c>
+      <c r="D48" t="s">
+        <v>138</v>
+      </c>
+      <c r="E48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F48" t="s">
+        <v>12</v>
+      </c>
+      <c r="G48">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rodríguez Román Leticia - Estadisticos 20221.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="133">
   <si>
     <t>Mat</t>
   </si>
@@ -76,7 +76,7 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>BAROJAS</t>
+    <t>IXMATLAHUA</t>
   </si>
   <si>
     <t>LOYO</t>
@@ -88,15 +88,9 @@
     <t>TERCERO</t>
   </si>
   <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
     <t>MATLATECATL</t>
   </si>
   <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
@@ -199,9 +193,6 @@
     <t>VENTURA</t>
   </si>
   <si>
-    <t>MONGE</t>
-  </si>
-  <si>
     <t>ROMERO</t>
   </si>
   <si>
@@ -211,9 +202,6 @@
     <t>CARRILLO</t>
   </si>
   <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
     <t>TZOPITL</t>
   </si>
   <si>
@@ -295,7 +283,7 @@
     <t>ROSALES</t>
   </si>
   <si>
-    <t>MARIEL</t>
+    <t>CRISTIAN FERNANDO</t>
   </si>
   <si>
     <t>DIEGO ARMANDO</t>
@@ -313,9 +301,6 @@
     <t>DULCE DANIELA</t>
   </si>
   <si>
-    <t>IVAN</t>
-  </si>
-  <si>
     <t>JOSE MANUEL</t>
   </si>
   <si>
@@ -326,9 +311,6 @@
   </si>
   <si>
     <t>CRISTIAN ALEXIS</t>
-  </si>
-  <si>
-    <t>CRISTIAN FERNANDO</t>
   </si>
   <si>
     <t>YAHIR</t>
@@ -1220,7 +1202,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1252,16 +1234,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920154</v>
+        <v>21330051920162</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1281,10 +1263,10 @@
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1304,10 +1286,10 @@
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1327,10 +1309,10 @@
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1347,13 +1329,13 @@
         <v>21330051920235</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1370,13 +1352,13 @@
         <v>21330051920240</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1390,16 +1372,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920188</v>
+        <v>19330061430023</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1413,16 +1395,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330061430023</v>
+        <v>21330051920202</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D9" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1436,16 +1418,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920202</v>
+        <v>21330051920203</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D10" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1459,39 +1441,39 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920203</v>
+        <v>21330051920152</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D11" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920152</v>
+        <v>21330051920171</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="D12" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1505,16 +1487,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920162</v>
+        <v>21330051920177</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="D13" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1528,16 +1510,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920171</v>
+        <v>21330051920181</v>
       </c>
       <c r="B14" t="s">
         <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="D14" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1551,22 +1533,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920177</v>
+        <v>21330051920251</v>
       </c>
       <c r="B15" t="s">
         <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D15" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1574,22 +1556,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920181</v>
+        <v>21330051920253</v>
       </c>
       <c r="B16" t="s">
         <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="D16" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1597,16 +1579,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920251</v>
+        <v>21330051920256</v>
       </c>
       <c r="B17" t="s">
         <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D17" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1620,16 +1602,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920253</v>
+        <v>21330051920257</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D18" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1643,16 +1625,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920256</v>
+        <v>21330051920081</v>
       </c>
       <c r="B19" t="s">
         <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D19" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1666,16 +1648,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920257</v>
+        <v>21330051920263</v>
       </c>
       <c r="B20" t="s">
         <v>36</v>
       </c>
       <c r="C20" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D20" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1689,16 +1671,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21330051920081</v>
+        <v>21330051920264</v>
       </c>
       <c r="B21" t="s">
         <v>37</v>
       </c>
       <c r="C21" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D21" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1712,16 +1694,13 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>21330051920263</v>
+        <v>21330051920267</v>
       </c>
       <c r="B22" t="s">
         <v>38</v>
       </c>
-      <c r="C22" t="s">
-        <v>74</v>
-      </c>
       <c r="D22" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1735,16 +1714,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>21330051920264</v>
+        <v>21330051920088</v>
       </c>
       <c r="B23" t="s">
         <v>39</v>
       </c>
       <c r="C23" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="D23" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -1758,13 +1737,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>21330051920267</v>
+        <v>21330051920358</v>
       </c>
       <c r="B24" t="s">
         <v>40</v>
       </c>
+      <c r="C24" t="s">
+        <v>24</v>
+      </c>
       <c r="D24" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -1778,16 +1760,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>21330051920088</v>
+        <v>21330051920361</v>
       </c>
       <c r="B25" t="s">
         <v>41</v>
       </c>
       <c r="C25" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D25" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -1801,16 +1783,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>21330051920358</v>
+        <v>21330051920362</v>
       </c>
       <c r="B26" t="s">
         <v>42</v>
       </c>
       <c r="C26" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="D26" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -1824,16 +1806,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>21330051920361</v>
+        <v>21330051920280</v>
       </c>
       <c r="B27" t="s">
         <v>43</v>
       </c>
       <c r="C27" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="D27" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -1847,16 +1829,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>21330051920362</v>
+        <v>21330051920284</v>
       </c>
       <c r="B28" t="s">
         <v>44</v>
       </c>
       <c r="C28" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D28" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -1870,16 +1852,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>21330051920280</v>
+        <v>21330051920285</v>
       </c>
       <c r="B29" t="s">
         <v>45</v>
       </c>
       <c r="C29" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="D29" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -1893,16 +1875,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>21330051920284</v>
+        <v>21330051920286</v>
       </c>
       <c r="B30" t="s">
         <v>46</v>
       </c>
       <c r="C30" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D30" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -1916,16 +1898,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>21330051920285</v>
+        <v>20330051920358</v>
       </c>
       <c r="B31" t="s">
         <v>47</v>
       </c>
       <c r="C31" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D31" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -1939,22 +1921,22 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>21330051920286</v>
+        <v>21330051920218</v>
       </c>
       <c r="B32" t="s">
         <v>48</v>
       </c>
       <c r="C32" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D32" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -1962,22 +1944,22 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>20330051920358</v>
+        <v>21330051920219</v>
       </c>
       <c r="B33" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C33" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="D33" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -1985,16 +1967,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>21330051920218</v>
+        <v>21330051920220</v>
       </c>
       <c r="B34" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C34" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D34" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -2008,16 +1990,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>21330051920219</v>
+        <v>21330051920230</v>
       </c>
       <c r="B35" t="s">
         <v>50</v>
       </c>
       <c r="C35" t="s">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="D35" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -2031,16 +2013,16 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>21330051920220</v>
+        <v>21330051920044</v>
       </c>
       <c r="B36" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="C36" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D36" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
@@ -2054,16 +2036,16 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>21330051920230</v>
+        <v>21330051920239</v>
       </c>
       <c r="B37" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C37" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D37" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
@@ -2077,16 +2059,16 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>21330051920044</v>
+        <v>21330051920247</v>
       </c>
       <c r="B38" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="C38" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D38" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
@@ -2100,16 +2082,16 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>21330051920239</v>
+        <v>21330051920250</v>
       </c>
       <c r="B39" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C39" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D39" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
@@ -2123,16 +2105,16 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>21330051920247</v>
+        <v>21330051920222</v>
       </c>
       <c r="B40" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C40" t="s">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="D40" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -2146,22 +2128,22 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>21330051920250</v>
+        <v>21330051920192</v>
       </c>
       <c r="B41" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C41" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D41" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
       </c>
       <c r="F41" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G41">
         <v>1</v>
@@ -2169,22 +2151,22 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>21330051920222</v>
+        <v>21330051920193</v>
       </c>
       <c r="B42" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="C42" t="s">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="D42" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
       </c>
       <c r="F42" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G42">
         <v>1</v>
@@ -2192,16 +2174,16 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>21330051920192</v>
+        <v>21330051920386</v>
       </c>
       <c r="B43" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C43" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D43" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
@@ -2215,16 +2197,16 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>21330051920193</v>
+        <v>21330051920199</v>
       </c>
       <c r="B44" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="C44" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="D44" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
@@ -2238,16 +2220,16 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>21330051920386</v>
+        <v>21330051920201</v>
       </c>
       <c r="B45" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C45" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D45" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -2261,16 +2243,16 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>21330051920199</v>
+        <v>21330051920213</v>
       </c>
       <c r="B46" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="C46" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="D46" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
@@ -2279,52 +2261,6 @@
         <v>12</v>
       </c>
       <c r="G46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47">
-        <v>21330051920201</v>
-      </c>
-      <c r="B47" t="s">
-        <v>58</v>
-      </c>
-      <c r="C47" t="s">
-        <v>90</v>
-      </c>
-      <c r="D47" t="s">
-        <v>137</v>
-      </c>
-      <c r="E47" t="s">
-        <v>8</v>
-      </c>
-      <c r="F47" t="s">
-        <v>12</v>
-      </c>
-      <c r="G47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48">
-        <v>21330051920213</v>
-      </c>
-      <c r="B48" t="s">
-        <v>59</v>
-      </c>
-      <c r="C48" t="s">
-        <v>91</v>
-      </c>
-      <c r="D48" t="s">
-        <v>138</v>
-      </c>
-      <c r="E48" t="s">
-        <v>8</v>
-      </c>
-      <c r="F48" t="s">
-        <v>12</v>
-      </c>
-      <c r="G48">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rodríguez Román Leticia - Estadisticos 20221.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="93">
   <si>
     <t>Mat</t>
   </si>
@@ -82,7 +82,7 @@
     <t>LOYO</t>
   </si>
   <si>
-    <t>HIDALGO</t>
+    <t>HERNANDEZ</t>
   </si>
   <si>
     <t>TERCERO</t>
@@ -112,171 +112,102 @@
     <t>TZITZIHUA</t>
   </si>
   <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>ARGÜELLO</t>
-  </si>
-  <si>
-    <t>ESPINOZA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>MADRAZO</t>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>MADRIGAL</t>
+  </si>
+  <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
+    <t>CHULIN</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>VICENTE</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>TZOPITL</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
   </si>
   <si>
     <t>MIXCOHUA</t>
   </si>
   <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>DE GANTE</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>MADRIGAL</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>CHULIN</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ARCADIO</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>TZOPITL</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>NARANJO</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>VICENTE</t>
-  </si>
-  <si>
-    <t>SORIANO</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>PORTILLA</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>DEL ROSARIO</t>
   </si>
   <si>
     <t>ARELLANO</t>
   </si>
   <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>DE GANTE</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>PORTILLA</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>DEL ROSARIO</t>
-  </si>
-  <si>
     <t>TZOMPAXTLE</t>
   </si>
   <si>
@@ -289,7 +220,7 @@
     <t>DIEGO ARMANDO</t>
   </si>
   <si>
-    <t>ANA LILIANA</t>
+    <t>ESTEFANIA</t>
   </si>
   <si>
     <t>MARIA DEL CARMEN</t>
@@ -320,57 +251,6 @@
   </si>
   <si>
     <t>ADALY</t>
-  </si>
-  <si>
-    <t>YARELI</t>
-  </si>
-  <si>
-    <t>ATZIN HEFZIBA</t>
-  </si>
-  <si>
-    <t>SUGHEYDI JAZMIN</t>
-  </si>
-  <si>
-    <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>ESTEFANIA</t>
-  </si>
-  <si>
-    <t>NADIA</t>
-  </si>
-  <si>
-    <t>VENUS</t>
-  </si>
-  <si>
-    <t>ANGELO RENE</t>
-  </si>
-  <si>
-    <t>ANGELINA</t>
-  </si>
-  <si>
-    <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>DUILIO</t>
-  </si>
-  <si>
-    <t>JAQUELINE</t>
-  </si>
-  <si>
-    <t>BETHSABE</t>
-  </si>
-  <si>
-    <t>RICARDO</t>
-  </si>
-  <si>
-    <t>FERNANDO</t>
-  </si>
-  <si>
-    <t>MAGDA SARAY</t>
-  </si>
-  <si>
-    <t>KARLA GRISELL</t>
   </si>
   <si>
     <t>YARETZI VALERIA</t>
@@ -1131,16 +1011,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="G3">
-        <v>51.22</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="H3">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1202,7 +1082,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1240,10 +1120,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1263,10 +1143,10 @@
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1280,16 +1160,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920262</v>
+        <v>21330051920081</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1309,10 +1189,10 @@
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1332,10 +1212,10 @@
         <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1358,7 +1238,7 @@
         <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1378,10 +1258,10 @@
         <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1401,10 +1281,10 @@
         <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1424,10 +1304,10 @@
         <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1447,10 +1327,10 @@
         <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1470,10 +1350,10 @@
         <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D12" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1493,10 +1373,10 @@
         <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="D13" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1519,7 +1399,7 @@
         <v>24</v>
       </c>
       <c r="D14" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1533,22 +1413,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920251</v>
+        <v>21330051920218</v>
       </c>
       <c r="B15" t="s">
         <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="D15" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1556,22 +1436,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920253</v>
+        <v>21330051920219</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C16" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="D16" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1579,22 +1459,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920256</v>
+        <v>21330051920220</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C17" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="D17" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1602,22 +1482,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920257</v>
+        <v>21330051920230</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C18" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="D18" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1625,22 +1505,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920081</v>
+        <v>21330051920044</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="C19" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="D19" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1648,22 +1528,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920263</v>
+        <v>21330051920239</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C20" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="D20" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1671,22 +1551,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21330051920264</v>
+        <v>21330051920247</v>
       </c>
       <c r="B21" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C21" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="D21" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1694,19 +1574,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>21330051920267</v>
+        <v>21330051920250</v>
       </c>
       <c r="B22" t="s">
-        <v>38</v>
+        <v>36</v>
+      </c>
+      <c r="C22" t="s">
+        <v>59</v>
       </c>
       <c r="D22" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1714,22 +1597,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>21330051920088</v>
+        <v>21330051920222</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C23" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="D23" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1737,22 +1620,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>21330051920358</v>
+        <v>21330051920192</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C24" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="D24" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1760,22 +1643,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>21330051920361</v>
+        <v>21330051920193</v>
       </c>
       <c r="B25" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="C25" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D25" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1783,22 +1666,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>21330051920362</v>
+        <v>21330051920386</v>
       </c>
       <c r="B26" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C26" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="D26" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -1806,22 +1689,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>21330051920280</v>
+        <v>21330051920199</v>
       </c>
       <c r="B27" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C27" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="D27" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -1829,22 +1712,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>21330051920284</v>
+        <v>21330051920201</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C28" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="D28" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -1852,415 +1735,24 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>21330051920285</v>
+        <v>21330051920213</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C29" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="D29" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>21330051920286</v>
-      </c>
-      <c r="B30" t="s">
-        <v>46</v>
-      </c>
-      <c r="C30" t="s">
-        <v>75</v>
-      </c>
-      <c r="D30" t="s">
-        <v>116</v>
-      </c>
-      <c r="E30" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" t="s">
-        <v>10</v>
-      </c>
-      <c r="G30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>20330051920358</v>
-      </c>
-      <c r="B31" t="s">
-        <v>47</v>
-      </c>
-      <c r="C31" t="s">
-        <v>76</v>
-      </c>
-      <c r="D31" t="s">
-        <v>117</v>
-      </c>
-      <c r="E31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" t="s">
-        <v>10</v>
-      </c>
-      <c r="G31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>21330051920218</v>
-      </c>
-      <c r="B32" t="s">
-        <v>48</v>
-      </c>
-      <c r="C32" t="s">
-        <v>77</v>
-      </c>
-      <c r="D32" t="s">
-        <v>118</v>
-      </c>
-      <c r="E32" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" t="s">
-        <v>11</v>
-      </c>
-      <c r="G32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>21330051920219</v>
-      </c>
-      <c r="B33" t="s">
-        <v>48</v>
-      </c>
-      <c r="C33" t="s">
-        <v>43</v>
-      </c>
-      <c r="D33" t="s">
-        <v>119</v>
-      </c>
-      <c r="E33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" t="s">
-        <v>11</v>
-      </c>
-      <c r="G33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>21330051920220</v>
-      </c>
-      <c r="B34" t="s">
-        <v>49</v>
-      </c>
-      <c r="C34" t="s">
-        <v>78</v>
-      </c>
-      <c r="D34" t="s">
-        <v>120</v>
-      </c>
-      <c r="E34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F34" t="s">
-        <v>11</v>
-      </c>
-      <c r="G34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>21330051920230</v>
-      </c>
-      <c r="B35" t="s">
-        <v>50</v>
-      </c>
-      <c r="C35" t="s">
-        <v>79</v>
-      </c>
-      <c r="D35" t="s">
-        <v>121</v>
-      </c>
-      <c r="E35" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" t="s">
-        <v>11</v>
-      </c>
-      <c r="G35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>21330051920044</v>
-      </c>
-      <c r="B36" t="s">
-        <v>35</v>
-      </c>
-      <c r="C36" t="s">
-        <v>80</v>
-      </c>
-      <c r="D36" t="s">
-        <v>122</v>
-      </c>
-      <c r="E36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" t="s">
-        <v>11</v>
-      </c>
-      <c r="G36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>21330051920239</v>
-      </c>
-      <c r="B37" t="s">
-        <v>51</v>
-      </c>
-      <c r="C37" t="s">
-        <v>81</v>
-      </c>
-      <c r="D37" t="s">
-        <v>123</v>
-      </c>
-      <c r="E37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" t="s">
-        <v>11</v>
-      </c>
-      <c r="G37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>21330051920247</v>
-      </c>
-      <c r="B38" t="s">
-        <v>52</v>
-      </c>
-      <c r="C38" t="s">
-        <v>82</v>
-      </c>
-      <c r="D38" t="s">
-        <v>124</v>
-      </c>
-      <c r="E38" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" t="s">
-        <v>11</v>
-      </c>
-      <c r="G38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>21330051920250</v>
-      </c>
-      <c r="B39" t="s">
-        <v>47</v>
-      </c>
-      <c r="C39" t="s">
-        <v>83</v>
-      </c>
-      <c r="D39" t="s">
-        <v>125</v>
-      </c>
-      <c r="E39" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" t="s">
-        <v>11</v>
-      </c>
-      <c r="G39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40">
-        <v>21330051920222</v>
-      </c>
-      <c r="B40" t="s">
-        <v>53</v>
-      </c>
-      <c r="C40" t="s">
-        <v>40</v>
-      </c>
-      <c r="D40" t="s">
-        <v>126</v>
-      </c>
-      <c r="E40" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" t="s">
-        <v>11</v>
-      </c>
-      <c r="G40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41">
-        <v>21330051920192</v>
-      </c>
-      <c r="B41" t="s">
-        <v>54</v>
-      </c>
-      <c r="C41" t="s">
-        <v>84</v>
-      </c>
-      <c r="D41" t="s">
-        <v>127</v>
-      </c>
-      <c r="E41" t="s">
-        <v>8</v>
-      </c>
-      <c r="F41" t="s">
-        <v>12</v>
-      </c>
-      <c r="G41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42">
-        <v>21330051920193</v>
-      </c>
-      <c r="B42" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" t="s">
-        <v>85</v>
-      </c>
-      <c r="D42" t="s">
-        <v>128</v>
-      </c>
-      <c r="E42" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" t="s">
-        <v>12</v>
-      </c>
-      <c r="G42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43">
-        <v>21330051920386</v>
-      </c>
-      <c r="B43" t="s">
-        <v>55</v>
-      </c>
-      <c r="C43" t="s">
-        <v>81</v>
-      </c>
-      <c r="D43" t="s">
-        <v>129</v>
-      </c>
-      <c r="E43" t="s">
-        <v>8</v>
-      </c>
-      <c r="F43" t="s">
-        <v>12</v>
-      </c>
-      <c r="G43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44">
-        <v>21330051920199</v>
-      </c>
-      <c r="B44" t="s">
-        <v>40</v>
-      </c>
-      <c r="C44" t="s">
-        <v>73</v>
-      </c>
-      <c r="D44" t="s">
-        <v>130</v>
-      </c>
-      <c r="E44" t="s">
-        <v>8</v>
-      </c>
-      <c r="F44" t="s">
-        <v>12</v>
-      </c>
-      <c r="G44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45">
-        <v>21330051920201</v>
-      </c>
-      <c r="B45" t="s">
-        <v>56</v>
-      </c>
-      <c r="C45" t="s">
-        <v>86</v>
-      </c>
-      <c r="D45" t="s">
-        <v>131</v>
-      </c>
-      <c r="E45" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" t="s">
-        <v>12</v>
-      </c>
-      <c r="G45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46">
-        <v>21330051920213</v>
-      </c>
-      <c r="B46" t="s">
-        <v>57</v>
-      </c>
-      <c r="C46" t="s">
-        <v>87</v>
-      </c>
-      <c r="D46" t="s">
-        <v>132</v>
-      </c>
-      <c r="E46" t="s">
-        <v>8</v>
-      </c>
-      <c r="F46" t="s">
-        <v>12</v>
-      </c>
-      <c r="G46">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rodríguez Román Leticia - Estadisticos 20221.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="80">
   <si>
     <t>Mat</t>
   </si>
@@ -79,151 +79,163 @@
     <t>IXMATLAHUA</t>
   </si>
   <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>TERCERO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>EVANGELISTA</t>
+  </si>
+  <si>
+    <t>ESPINOSA</t>
+  </si>
+  <si>
     <t>LOYO</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>TERCERO</t>
+    <t>MOLOHUA</t>
+  </si>
+  <si>
+    <t>TZITZIHUA</t>
   </si>
   <si>
     <t>MATLATECATL</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>NERI</t>
+  </si>
+  <si>
+    <t>VICENTE</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>TZOPITL</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
   </si>
   <si>
     <t>PALOMARES</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
-    <t>SAN JUAN</t>
-  </si>
-  <si>
-    <t>TZITZIHUA</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>MADRIGAL</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>CHULIN</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>VICENTE</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>TZOPITL</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>DE GANTE</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
     <t>PORTILLA</t>
   </si>
   <si>
-    <t>RICO</t>
-  </si>
-  <si>
     <t>DEL ROSARIO</t>
   </si>
   <si>
     <t>ARELLANO</t>
   </si>
   <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
     <t>CRISTIAN FERNANDO</t>
   </si>
   <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>ESTEFANIA</t>
+  </si>
+  <si>
+    <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>LORENA</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
+  </si>
+  <si>
+    <t>DIEGO ANTONIO</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>ANGEL DANIEL</t>
+  </si>
+  <si>
+    <t>CRISTIAN ALEXIS</t>
+  </si>
+  <si>
+    <t>JUAN GERARDO</t>
+  </si>
+  <si>
+    <t>ALEXANDER</t>
+  </si>
+  <si>
     <t>DIEGO ARMANDO</t>
   </si>
   <si>
-    <t>ESTEFANIA</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
+    <t>YAHIR</t>
+  </si>
+  <si>
+    <t>ADALY</t>
+  </si>
+  <si>
+    <t>ARANZA DANAE</t>
   </si>
   <si>
     <t>LIZBETH JOSELYN</t>
@@ -232,57 +244,12 @@
     <t>DULCE DANIELA</t>
   </si>
   <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>JOSE ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ANGEL DANIEL</t>
-  </si>
-  <si>
-    <t>CRISTIAN ALEXIS</t>
-  </si>
-  <si>
-    <t>YAHIR</t>
-  </si>
-  <si>
-    <t>ANGEL FIDEL</t>
-  </si>
-  <si>
-    <t>ADALY</t>
-  </si>
-  <si>
-    <t>YARETZI VALERIA</t>
-  </si>
-  <si>
-    <t>JESUS MANUEL</t>
-  </si>
-  <si>
-    <t>LAURA EVELYN</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>ARANZA DANAE</t>
-  </si>
-  <si>
-    <t>AMERICA PAOLA</t>
-  </si>
-  <si>
-    <t>CITLALI</t>
-  </si>
-  <si>
     <t>GETSEMANI GUADALUPE</t>
   </si>
   <si>
     <t>YAEL</t>
   </si>
   <si>
-    <t>CESAR SAID</t>
-  </si>
-  <si>
     <t>JASIEL</t>
   </si>
   <si>
@@ -290,12 +257,6 @@
   </si>
   <si>
     <t>WENCESLAO</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
   </si>
 </sst>
 </file>
@@ -985,16 +946,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>68.75</v>
+        <v>62.5</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1037,16 +998,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G4">
-        <v>61.54</v>
+        <v>74.36</v>
       </c>
       <c r="H4">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1063,16 +1024,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F5">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G5">
-        <v>58.06</v>
+        <v>70.97</v>
       </c>
       <c r="H5">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
     </row>
   </sheetData>
@@ -1082,7 +1043,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1120,10 +1081,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1137,16 +1098,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920164</v>
+        <v>21330051920165</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1160,22 +1121,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920081</v>
+        <v>21330051920166</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1183,16 +1144,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920282</v>
+        <v>21330051920081</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1206,22 +1167,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920235</v>
+        <v>21330051920282</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1229,16 +1190,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920240</v>
+        <v>21330051920234</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1252,22 +1213,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330061430023</v>
+        <v>21330051920359</v>
       </c>
       <c r="B8" t="s">
         <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1275,22 +1236,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920202</v>
+        <v>21330051920237</v>
       </c>
       <c r="B9" t="s">
         <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1298,16 +1259,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920203</v>
+        <v>19330061430023</v>
       </c>
       <c r="B10" t="s">
         <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1321,39 +1282,39 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920152</v>
+        <v>21330051920203</v>
       </c>
       <c r="B11" t="s">
         <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920171</v>
+        <v>21330051920152</v>
       </c>
       <c r="B12" t="s">
         <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1367,16 +1328,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920177</v>
+        <v>21330051920156</v>
       </c>
       <c r="B13" t="s">
         <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1390,16 +1351,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920181</v>
+        <v>21330051920157</v>
       </c>
       <c r="B14" t="s">
         <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1413,22 +1374,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920218</v>
+        <v>21330051920164</v>
       </c>
       <c r="B15" t="s">
         <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1436,22 +1397,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920219</v>
+        <v>21330051920171</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D16" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1459,22 +1420,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920220</v>
+        <v>21330051920181</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="D17" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1482,16 +1443,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920230</v>
+        <v>21330051920044</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D18" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1505,16 +1466,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920044</v>
+        <v>21330051920235</v>
       </c>
       <c r="B19" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C19" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D19" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1528,16 +1489,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920239</v>
+        <v>21330051920240</v>
       </c>
       <c r="B20" t="s">
         <v>34</v>
       </c>
       <c r="C20" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D20" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1551,16 +1512,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21330051920247</v>
+        <v>21330051920250</v>
       </c>
       <c r="B21" t="s">
         <v>35</v>
       </c>
       <c r="C21" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D21" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1574,16 +1535,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>21330051920250</v>
+        <v>21330051920222</v>
       </c>
       <c r="B22" t="s">
         <v>36</v>
       </c>
       <c r="C22" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="D22" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1597,22 +1558,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>21330051920222</v>
+        <v>21330051920193</v>
       </c>
       <c r="B23" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C23" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="D23" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1620,16 +1581,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>21330051920192</v>
+        <v>21330051920386</v>
       </c>
       <c r="B24" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="C24" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="D24" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -1643,16 +1604,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>21330051920193</v>
+        <v>21330051920199</v>
       </c>
       <c r="B25" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="C25" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D25" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -1661,98 +1622,6 @@
         <v>12</v>
       </c>
       <c r="G25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>21330051920386</v>
-      </c>
-      <c r="B26" t="s">
-        <v>39</v>
-      </c>
-      <c r="C26" t="s">
-        <v>57</v>
-      </c>
-      <c r="D26" t="s">
-        <v>89</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>12</v>
-      </c>
-      <c r="G26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>21330051920199</v>
-      </c>
-      <c r="B27" t="s">
-        <v>40</v>
-      </c>
-      <c r="C27" t="s">
-        <v>62</v>
-      </c>
-      <c r="D27" t="s">
-        <v>90</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>12</v>
-      </c>
-      <c r="G27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>21330051920201</v>
-      </c>
-      <c r="B28" t="s">
-        <v>41</v>
-      </c>
-      <c r="C28" t="s">
-        <v>63</v>
-      </c>
-      <c r="D28" t="s">
-        <v>91</v>
-      </c>
-      <c r="E28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" t="s">
-        <v>12</v>
-      </c>
-      <c r="G28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>21330051920213</v>
-      </c>
-      <c r="B29" t="s">
-        <v>42</v>
-      </c>
-      <c r="C29" t="s">
-        <v>64</v>
-      </c>
-      <c r="D29" t="s">
-        <v>92</v>
-      </c>
-      <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" t="s">
-        <v>12</v>
-      </c>
-      <c r="G29">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rodríguez Román Leticia - Estadisticos 20221.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20221.xlsx
@@ -145,33 +145,33 @@
     <t>CARRILLO</t>
   </si>
   <si>
+    <t>TZOPITL</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
     <t>VASQUEZ</t>
   </si>
   <si>
-    <t>TZOPITL</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
     <t>CRUZ</t>
   </si>
   <si>
@@ -202,40 +202,40 @@
     <t>MARIA DEL CARMEN</t>
   </si>
   <si>
+    <t>EDUARDO</t>
+  </si>
+  <si>
+    <t>DIEGO ANTONIO</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>ANGEL DANIEL</t>
+  </si>
+  <si>
+    <t>CRISTIAN ALEXIS</t>
+  </si>
+  <si>
+    <t>JUAN GERARDO</t>
+  </si>
+  <si>
+    <t>ALEXANDER</t>
+  </si>
+  <si>
+    <t>DIEGO ARMANDO</t>
+  </si>
+  <si>
+    <t>YAHIR</t>
+  </si>
+  <si>
+    <t>ADALY</t>
+  </si>
+  <si>
+    <t>ARANZA DANAE</t>
+  </si>
+  <si>
     <t>LORENA</t>
-  </si>
-  <si>
-    <t>EDUARDO</t>
-  </si>
-  <si>
-    <t>DIEGO ANTONIO</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>ANGEL DANIEL</t>
-  </si>
-  <si>
-    <t>CRISTIAN ALEXIS</t>
-  </si>
-  <si>
-    <t>JUAN GERARDO</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>DIEGO ARMANDO</t>
-  </si>
-  <si>
-    <t>YAHIR</t>
-  </si>
-  <si>
-    <t>ADALY</t>
-  </si>
-  <si>
-    <t>ARANZA DANAE</t>
   </si>
   <si>
     <t>LIZBETH JOSELYN</t>
@@ -1190,13 +1190,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920234</v>
+        <v>21330051920359</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
         <v>61</v>
@@ -1213,13 +1213,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920359</v>
+        <v>21330051920237</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
         <v>62</v>
@@ -1236,13 +1236,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920237</v>
+        <v>19330061430023</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
         <v>63</v>
@@ -1251,7 +1251,7 @@
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1259,10 +1259,10 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330061430023</v>
+        <v>21330051920203</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
         <v>43</v>
@@ -1282,10 +1282,10 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920203</v>
+        <v>21330051920152</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
         <v>44</v>
@@ -1297,18 +1297,18 @@
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920152</v>
+        <v>21330051920156</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
         <v>45</v>
@@ -1328,10 +1328,10 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920156</v>
+        <v>21330051920157</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
         <v>46</v>
@@ -1351,10 +1351,10 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920157</v>
+        <v>21330051920164</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
         <v>47</v>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920164</v>
+        <v>21330051920171</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
         <v>48</v>
@@ -1397,13 +1397,13 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920171</v>
+        <v>21330051920181</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="D16" t="s">
         <v>70</v>
@@ -1420,13 +1420,13 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920181</v>
+        <v>21330051920044</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s">
         <v>71</v>
@@ -1435,7 +1435,7 @@
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1443,7 +1443,7 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920044</v>
+        <v>21330051920234</v>
       </c>
       <c r="B18" t="s">
         <v>22</v>
